--- a/data/trans_bre/IP22_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP22_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 8,01</t>
+          <t>-17,51; 7,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,88; -0,29</t>
+          <t>-29,15; 0,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 17,23</t>
+          <t>-10,16; 18,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 27,12</t>
+          <t>-4,13; 26,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-48,54; 38,19</t>
+          <t>-49,3; 30,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-55,32; 0,74</t>
+          <t>-55,44; 1,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,59; 64,15</t>
+          <t>-25,31; 67,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 133,97</t>
+          <t>-17,34; 132,84</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 4,56</t>
+          <t>-13,86; 4,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 5,68</t>
+          <t>-14,42; 6,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 11,67</t>
+          <t>-7,59; 11,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 9,61</t>
+          <t>-9,64; 10,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 23,79</t>
+          <t>-47,61; 22,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,88; 19,08</t>
+          <t>-35,0; 24,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 55,34</t>
+          <t>-25,44; 56,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,77; 111,77</t>
+          <t>-55,73; 117,66</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 9,67</t>
+          <t>-12,91; 9,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 13,31</t>
+          <t>-13,73; 12,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 11,74</t>
+          <t>-2,76; 11,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 20,01</t>
+          <t>-0,92; 21,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,44; 55,95</t>
+          <t>-45,48; 54,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 52,45</t>
+          <t>-35,85; 45,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-45,57; 841,03</t>
+          <t>-52,09; 619,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 221,16</t>
+          <t>-12,11; 257,31</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 8,4</t>
+          <t>-12,28; 9,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 7,26</t>
+          <t>-16,69; 7,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 2,61</t>
+          <t>-21,84; 3,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 11,76</t>
+          <t>-14,73; 12,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,46; 47,87</t>
+          <t>-43,02; 58,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,49; 33,28</t>
+          <t>-46,33; 32,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,86; 10,13</t>
+          <t>-52,48; 11,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,79; 119,12</t>
+          <t>-55,0; 124,17</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 12,72</t>
+          <t>-11,71; 12,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 25,49</t>
+          <t>-3,67; 28,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 17,49</t>
+          <t>0,4; 17,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 7,62</t>
+          <t>-9,97; 5,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-60,48; 179,98</t>
+          <t>-58,5; 165,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 131,81</t>
+          <t>-10,82; 162,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-40,07; —</t>
+          <t>-32,83; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 378,16</t>
+          <t>-100,0; 214,66</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 10,68</t>
+          <t>-14,79; 10,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 8,7</t>
+          <t>-21,07; 8,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 18,83</t>
+          <t>-5,98; 18,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 7,13</t>
+          <t>-13,6; 7,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,02; 70,06</t>
+          <t>-48,77; 53,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 33,17</t>
+          <t>-47,8; 31,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 200,6</t>
+          <t>-26,5; 194,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,69; 76,37</t>
+          <t>-62,96; 81,13</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 8,57</t>
+          <t>-8,11; 8,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 1,15</t>
+          <t>-15,64; 2,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 8,47</t>
+          <t>-2,08; 8,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 4,88</t>
+          <t>-15,25; 3,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-30,41; 45,87</t>
+          <t>-30,84; 49,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-45,82; 5,43</t>
+          <t>-46,57; 9,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 153,59</t>
+          <t>-24,27; 165,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-47,82; 25,32</t>
+          <t>-50,44; 19,52</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 2,99</t>
+          <t>-10,02; 2,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 3,98</t>
+          <t>-6,23; 3,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 2,68</t>
+          <t>-8,36; 2,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 1,55</t>
+          <t>-5,9; 1,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,45; 23,96</t>
+          <t>-50,87; 21,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,8; 68,58</t>
+          <t>-53,85; 59,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-53,24; 27,75</t>
+          <t>-53,33; 25,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-81,67; 61,42</t>
+          <t>-79,16; 69,28</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 1,05</t>
+          <t>-5,75; 0,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,6; -0,11</t>
+          <t>-7,8; -0,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 4,08</t>
+          <t>-2,53; 4,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,05</t>
+          <t>-3,7; 4,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 5,33</t>
+          <t>-25,19; 3,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,64; 0,04</t>
+          <t>-26,5; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 27,05</t>
+          <t>-13,6; 25,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 29,0</t>
+          <t>-22,11; 31,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP22_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP22_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,84</t>
+          <t>6,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 7,35</t>
+          <t>-18,65; 8,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 0,42</t>
+          <t>-27,62; -0,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 18,52</t>
+          <t>-11,93; 17,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 26,7</t>
+          <t>-7,11; 20,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 30,3</t>
+          <t>-49,74; 32,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-55,44; 1,19</t>
+          <t>-54,84; -1,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 67,63</t>
+          <t>-29,06; 67,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 132,84</t>
+          <t>-22,06; 107,44</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>44,73%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 4,14</t>
+          <t>-13,81; 5,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 6,97</t>
+          <t>-15,96; 5,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 11,83</t>
+          <t>-7,13; 11,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 10,17</t>
+          <t>-3,96; 14,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,61; 22,38</t>
+          <t>-46,35; 27,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 24,31</t>
+          <t>-38,23; 19,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 56,02</t>
+          <t>-23,75; 56,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,73; 117,66</t>
+          <t>-27,48; 175,49</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,09</t>
+          <t>8,61</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>67,98%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 9,85</t>
+          <t>-12,53; 11,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 12,26</t>
+          <t>-15,21; 11,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 11,37</t>
+          <t>-2,61; 11,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 21,39</t>
+          <t>-1,6; 19,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,48; 54,15</t>
+          <t>-42,64; 64,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,85; 45,58</t>
+          <t>-39,38; 41,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-52,09; 619,18</t>
+          <t>-59,97; 714,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 257,31</t>
+          <t>-12,79; 247,95</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-5,24%</t>
+          <t>-2,36%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 9,36</t>
+          <t>-11,86; 9,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 7,52</t>
+          <t>-15,23; 8,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 3,03</t>
+          <t>-20,91; 2,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 12,96</t>
+          <t>-14,96; 13,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 58,12</t>
+          <t>-42,18; 60,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 32,74</t>
+          <t>-44,67; 41,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,48; 11,44</t>
+          <t>-51,08; 10,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,0; 124,17</t>
+          <t>-54,18; 147,03</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,71</t>
+          <t>-2,61</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-25,39%</t>
+          <t>-37,97%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 12,56</t>
+          <t>-11,8; 13,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 28,15</t>
+          <t>-4,94; 27,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 17,94</t>
+          <t>0,87; 18,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 5,85</t>
+          <t>-11,1; 4,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-58,5; 165,95</t>
+          <t>-60,67; 189,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 162,64</t>
+          <t>-15,61; 143,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,83; —</t>
+          <t>-48,52; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 214,66</t>
+          <t>-100,0; 272,48</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,08</t>
+          <t>-2,61</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-19,02%</t>
+          <t>-16,71%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 10,41</t>
+          <t>-13,91; 12,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 8,96</t>
+          <t>-20,5; 9,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 18,87</t>
+          <t>-6,21; 19,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 7,97</t>
+          <t>-12,95; 8,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,77; 53,03</t>
+          <t>-46,81; 76,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 31,67</t>
+          <t>-47,64; 34,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 194,76</t>
+          <t>-29,45; 197,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-62,96; 81,13</t>
+          <t>-63,05; 83,0</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,7</t>
+          <t>-6,35</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-22,43%</t>
+          <t>-24,59%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 8,96</t>
+          <t>-7,28; 8,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 2,17</t>
+          <t>-15,03; 2,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 8,81</t>
+          <t>-2,36; 8,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 3,55</t>
+          <t>-16,03; 2,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 49,22</t>
+          <t>-28,82; 45,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 9,74</t>
+          <t>-45,91; 9,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 165,25</t>
+          <t>-27,3; 164,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-50,44; 19,52</t>
+          <t>-53,08; 13,26</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>-1,51</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-36,78%</t>
+          <t>-33,38%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 2,81</t>
+          <t>-9,84; 2,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 3,69</t>
+          <t>-5,46; 3,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 2,55</t>
+          <t>-8,12; 2,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 1,46</t>
+          <t>-5,48; 1,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,87; 21,8</t>
+          <t>-50,45; 21,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,85; 59,2</t>
+          <t>-51,65; 65,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-53,33; 25,19</t>
+          <t>-53,13; 26,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-79,16; 69,28</t>
+          <t>-80,66; 83,92</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 0,69</t>
+          <t>-5,68; 1,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,8; -0,05</t>
+          <t>-7,63; -0,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,04</t>
+          <t>-2,54; 3,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 4,26</t>
+          <t>-3,39; 3,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 3,69</t>
+          <t>-23,91; 5,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 0,0</t>
+          <t>-26,0; -2,41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 25,62</t>
+          <t>-13,56; 25,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 31,36</t>
+          <t>-19,9; 23,22</t>
         </is>
       </c>
     </row>
